--- a/countries/cn-xz/2000-2004.xlsx
+++ b/countries/cn-xz/2000-2004.xlsx
@@ -765,9 +765,12 @@
       <c r="O2" t="n">
         <v>54</v>
       </c>
+      <c r="R2" t="n">
+        <v>1.956521739130435</v>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -1155,9 +1158,12 @@
       <c r="O4" t="n">
         <v>20</v>
       </c>
+      <c r="R4" t="n">
+        <v>0.7246376811594203</v>
+      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1545,9 +1551,12 @@
       <c r="O6" t="n">
         <v>225</v>
       </c>
+      <c r="R6" t="n">
+        <v>8.152173913043478</v>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1935,9 +1944,12 @@
       <c r="O8" t="n">
         <v>222</v>
       </c>
+      <c r="R8" t="n">
+        <v>8.043478260869566</v>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -2325,9 +2337,12 @@
       <c r="O10" t="n">
         <v>4</v>
       </c>
+      <c r="R10" t="n">
+        <v>0.1449275362318841</v>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -2715,9 +2730,12 @@
       <c r="O12" t="n">
         <v>10</v>
       </c>
+      <c r="R12" t="n">
+        <v>0.3623188405797101</v>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -3105,9 +3123,12 @@
       <c r="O14" t="n">
         <v>50</v>
       </c>
+      <c r="R14" t="n">
+        <v>1.811594202898551</v>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -3495,9 +3516,12 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
+      <c r="R16" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -3885,9 +3909,12 @@
       <c r="O18" t="n">
         <v>18</v>
       </c>
+      <c r="R18" t="n">
+        <v>0.6521739130434783</v>
+      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -4275,9 +4302,12 @@
       <c r="O20" t="n">
         <v>21</v>
       </c>
+      <c r="R20" t="n">
+        <v>0.7608695652173914</v>
+      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -4665,9 +4695,12 @@
       <c r="O22" t="n">
         <v>166</v>
       </c>
+      <c r="R22" t="n">
+        <v>6.014492753623188</v>
+      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -5055,9 +5088,12 @@
       <c r="O24" t="n">
         <v>187</v>
       </c>
+      <c r="R24" t="n">
+        <v>6.77536231884058</v>
+      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -5445,9 +5481,12 @@
       <c r="O26" t="n">
         <v>9</v>
       </c>
+      <c r="R26" t="n">
+        <v>0.3260869565217391</v>
+      </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -5835,9 +5874,12 @@
       <c r="O28" t="n">
         <v>6</v>
       </c>
+      <c r="R28" t="n">
+        <v>0.2173913043478261</v>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -6225,9 +6267,12 @@
       <c r="O30" t="n">
         <v>10</v>
       </c>
+      <c r="R30" t="n">
+        <v>0.3623188405797101</v>
+      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -6615,9 +6660,12 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
+      <c r="R32" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -7005,9 +7053,12 @@
       <c r="O34" t="n">
         <v>28</v>
       </c>
+      <c r="R34" t="n">
+        <v>1.014492753623188</v>
+      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -7395,9 +7446,12 @@
       <c r="O36" t="n">
         <v>35</v>
       </c>
+      <c r="R36" t="n">
+        <v>1.268115942028986</v>
+      </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -7785,9 +7839,12 @@
       <c r="O38" t="n">
         <v>314</v>
       </c>
+      <c r="R38" t="n">
+        <v>11.3768115942029</v>
+      </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -8175,9 +8232,12 @@
       <c r="O40" t="n">
         <v>195</v>
       </c>
+      <c r="R40" t="n">
+        <v>7.065217391304347</v>
+      </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -8565,9 +8625,12 @@
       <c r="O42" t="n">
         <v>2</v>
       </c>
+      <c r="R42" t="n">
+        <v>0.07246376811594203</v>
+      </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -8955,9 +9018,12 @@
       <c r="O44" t="n">
         <v>18</v>
       </c>
+      <c r="R44" t="n">
+        <v>0.6521739130434783</v>
+      </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -9345,9 +9411,12 @@
       <c r="O46" t="n">
         <v>13</v>
       </c>
+      <c r="R46" t="n">
+        <v>0.4710144927536232</v>
+      </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -9735,9 +9804,12 @@
       <c r="O48" t="n">
         <v>15</v>
       </c>
+      <c r="R48" t="n">
+        <v>0.5434782608695653</v>
+      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -10125,9 +10197,12 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
+      <c r="R50" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -10515,9 +10590,12 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
+      <c r="R52" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -10905,9 +10983,12 @@
       <c r="O54" t="n">
         <v>22</v>
       </c>
+      <c r="R54" t="n">
+        <v>0.7971014492753623</v>
+      </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -11295,9 +11376,12 @@
       <c r="O56" t="n">
         <v>26</v>
       </c>
+      <c r="R56" t="n">
+        <v>0.9420289855072465</v>
+      </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -11685,9 +11769,12 @@
       <c r="O58" t="n">
         <v>254</v>
       </c>
+      <c r="R58" t="n">
+        <v>9.202898550724637</v>
+      </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -12075,9 +12162,12 @@
       <c r="O60" t="n">
         <v>191</v>
       </c>
+      <c r="R60" t="n">
+        <v>6.920289855072464</v>
+      </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -12465,9 +12555,12 @@
       <c r="O62" t="n">
         <v>13</v>
       </c>
+      <c r="R62" t="n">
+        <v>0.4710144927536232</v>
+      </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -12855,9 +12948,12 @@
       <c r="O64" t="n">
         <v>22</v>
       </c>
+      <c r="R64" t="n">
+        <v>0.7971014492753623</v>
+      </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -13245,9 +13341,12 @@
       <c r="O66" t="n">
         <v>13</v>
       </c>
+      <c r="R66" t="n">
+        <v>0.4710144927536232</v>
+      </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -13635,9 +13734,12 @@
       <c r="O68" t="n">
         <v>32</v>
       </c>
+      <c r="R68" t="n">
+        <v>1.159420289855073</v>
+      </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -14025,9 +14127,12 @@
       <c r="O70" t="n">
         <v>2</v>
       </c>
+      <c r="R70" t="n">
+        <v>0.07246376811594203</v>
+      </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -14415,9 +14520,12 @@
       <c r="O72" t="n">
         <v>29</v>
       </c>
+      <c r="R72" t="n">
+        <v>1.050724637681159</v>
+      </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -14805,9 +14913,12 @@
       <c r="O74" t="n">
         <v>31</v>
       </c>
+      <c r="R74" t="n">
+        <v>1.123188405797101</v>
+      </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -15195,9 +15306,12 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
+      <c r="R76" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -15585,9 +15699,12 @@
       <c r="O78" t="n">
         <v>205</v>
       </c>
+      <c r="R78" t="n">
+        <v>7.427536231884059</v>
+      </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -15975,9 +16092,12 @@
       <c r="O80" t="n">
         <v>215</v>
       </c>
+      <c r="R80" t="n">
+        <v>7.789855072463768</v>
+      </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -16365,9 +16485,12 @@
       <c r="O82" t="n">
         <v>2</v>
       </c>
+      <c r="R82" t="n">
+        <v>0.07246376811594203</v>
+      </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -16755,9 +16878,12 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
+      <c r="R84" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -17145,9 +17271,12 @@
       <c r="O86" t="n">
         <v>53</v>
       </c>
+      <c r="R86" t="n">
+        <v>1.920289855072464</v>
+      </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -17535,9 +17664,12 @@
       <c r="O88" t="n">
         <v>10</v>
       </c>
+      <c r="R88" t="n">
+        <v>0.3623188405797101</v>
+      </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -17925,9 +18057,12 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
+      <c r="R90" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -18315,9 +18450,12 @@
       <c r="O92" t="n">
         <v>33</v>
       </c>
+      <c r="R92" t="n">
+        <v>1.195652173913043</v>
+      </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -18705,9 +18843,12 @@
       <c r="O94" t="n">
         <v>33</v>
       </c>
+      <c r="R94" t="n">
+        <v>1.195652173913043</v>
+      </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -19095,9 +19236,12 @@
       <c r="O96" t="n">
         <v>19</v>
       </c>
+      <c r="R96" t="n">
+        <v>0.6884057971014492</v>
+      </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -19485,9 +19629,12 @@
       <c r="O98" t="n">
         <v>296</v>
       </c>
+      <c r="R98" t="n">
+        <v>10.72463768115942</v>
+      </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -19875,9 +20022,12 @@
       <c r="O100" t="n">
         <v>193</v>
       </c>
+      <c r="R100" t="n">
+        <v>6.992753623188406</v>
+      </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -20265,9 +20415,12 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -20655,9 +20808,12 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
+      <c r="R104" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -21045,9 +21201,12 @@
       <c r="O106" t="n">
         <v>104</v>
       </c>
+      <c r="R106" t="n">
+        <v>3.768115942028986</v>
+      </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -21435,9 +21594,12 @@
       <c r="O108" t="n">
         <v>10</v>
       </c>
+      <c r="R108" t="n">
+        <v>0.3623188405797101</v>
+      </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -21825,9 +21987,12 @@
       <c r="O110" t="n">
         <v>22</v>
       </c>
+      <c r="R110" t="n">
+        <v>0.7971014492753623</v>
+      </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -22215,9 +22380,12 @@
       <c r="O112" t="n">
         <v>4</v>
       </c>
+      <c r="R112" t="n">
+        <v>0.1449275362318841</v>
+      </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -22605,9 +22773,12 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
+      <c r="R114" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -22995,9 +23166,12 @@
       <c r="O116" t="n">
         <v>38</v>
       </c>
+      <c r="R116" t="n">
+        <v>1.376811594202898</v>
+      </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -23385,9 +23559,12 @@
       <c r="O118" t="n">
         <v>27</v>
       </c>
+      <c r="R118" t="n">
+        <v>0.9782608695652175</v>
+      </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -23775,9 +23952,12 @@
       <c r="O120" t="n">
         <v>234</v>
       </c>
+      <c r="R120" t="n">
+        <v>8.478260869565219</v>
+      </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -24165,9 +24345,12 @@
       <c r="O122" t="n">
         <v>166</v>
       </c>
+      <c r="R122" t="n">
+        <v>6.014492753623188</v>
+      </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -24555,9 +24738,12 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
+      <c r="R124" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -24945,9 +25131,12 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
+      <c r="R126" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -25335,9 +25524,12 @@
       <c r="O128" t="n">
         <v>17</v>
       </c>
+      <c r="R128" t="n">
+        <v>0.6159420289855072</v>
+      </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -25725,9 +25917,12 @@
       <c r="O130" t="n">
         <v>1</v>
       </c>
+      <c r="R130" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -26115,9 +26310,12 @@
       <c r="O132" t="n">
         <v>8</v>
       </c>
+      <c r="R132" t="n">
+        <v>0.2898550724637681</v>
+      </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -26505,9 +26703,12 @@
       <c r="O134" t="n">
         <v>14</v>
       </c>
+      <c r="R134" t="n">
+        <v>0.5072463768115942</v>
+      </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -26895,9 +27096,12 @@
       <c r="O136" t="n">
         <v>3</v>
       </c>
+      <c r="R136" t="n">
+        <v>0.108695652173913</v>
+      </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -27285,9 +27489,12 @@
       <c r="O138" t="n">
         <v>22</v>
       </c>
+      <c r="R138" t="n">
+        <v>0.7971014492753623</v>
+      </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
@@ -27675,9 +27882,12 @@
       <c r="O140" t="n">
         <v>29</v>
       </c>
+      <c r="R140" t="n">
+        <v>1.050724637681159</v>
+      </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -28065,9 +28275,12 @@
       <c r="O142" t="n">
         <v>29</v>
       </c>
+      <c r="R142" t="n">
+        <v>1.050724637681159</v>
+      </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -28455,9 +28668,12 @@
       <c r="O144" t="n">
         <v>304</v>
       </c>
+      <c r="R144" t="n">
+        <v>11.01449275362319</v>
+      </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
@@ -28845,9 +29061,12 @@
       <c r="O146" t="n">
         <v>161</v>
       </c>
+      <c r="R146" t="n">
+        <v>5.833333333333333</v>
+      </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
@@ -29235,9 +29454,12 @@
       <c r="O148" t="n">
         <v>1</v>
       </c>
+      <c r="R148" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
@@ -29625,9 +29847,12 @@
       <c r="O150" t="n">
         <v>25</v>
       </c>
+      <c r="R150" t="n">
+        <v>0.9057971014492754</v>
+      </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
@@ -30015,9 +30240,12 @@
       <c r="O152" t="n">
         <v>2</v>
       </c>
+      <c r="R152" t="n">
+        <v>0.07246376811594203</v>
+      </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -30405,9 +30633,12 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
+      <c r="R154" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
@@ -30795,9 +31026,12 @@
       <c r="O156" t="n">
         <v>7</v>
       </c>
+      <c r="R156" t="n">
+        <v>0.2536231884057971</v>
+      </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -31185,9 +31419,12 @@
       <c r="O158" t="n">
         <v>9</v>
       </c>
+      <c r="R158" t="n">
+        <v>0.3260869565217391</v>
+      </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U158" t="inlineStr">
@@ -31575,9 +31812,12 @@
       <c r="O160" t="n">
         <v>30</v>
       </c>
+      <c r="R160" t="n">
+        <v>1.086956521739131</v>
+      </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U160" t="inlineStr">
@@ -31965,9 +32205,12 @@
       <c r="O162" t="n">
         <v>21</v>
       </c>
+      <c r="R162" t="n">
+        <v>0.7608695652173914</v>
+      </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
@@ -32355,9 +32598,12 @@
       <c r="O164" t="n">
         <v>251</v>
       </c>
+      <c r="R164" t="n">
+        <v>9.094202898550725</v>
+      </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U164" t="inlineStr">
@@ -32745,9 +32991,12 @@
       <c r="O166" t="n">
         <v>140</v>
       </c>
+      <c r="R166" t="n">
+        <v>5.072463768115942</v>
+      </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
@@ -33135,9 +33384,12 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
+      <c r="R168" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U168" t="inlineStr">
@@ -33525,9 +33777,12 @@
       <c r="O170" t="n">
         <v>5</v>
       </c>
+      <c r="R170" t="n">
+        <v>0.1811594202898551</v>
+      </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U170" t="inlineStr">
@@ -33915,9 +34170,12 @@
       <c r="O172" t="n">
         <v>1</v>
       </c>
+      <c r="R172" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U172" t="inlineStr">
@@ -34305,9 +34563,12 @@
       <c r="O174" t="n">
         <v>1</v>
       </c>
+      <c r="R174" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U174" t="inlineStr">
@@ -34695,9 +34956,12 @@
       <c r="O176" t="n">
         <v>23</v>
       </c>
+      <c r="R176" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U176" t="inlineStr">
@@ -35085,9 +35349,12 @@
       <c r="O178" t="n">
         <v>1</v>
       </c>
+      <c r="R178" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U178" t="inlineStr">
@@ -35475,9 +35742,12 @@
       <c r="O180" t="n">
         <v>18</v>
       </c>
+      <c r="R180" t="n">
+        <v>0.6521739130434783</v>
+      </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U180" t="inlineStr">
@@ -35865,9 +36135,12 @@
       <c r="O182" t="n">
         <v>68</v>
       </c>
+      <c r="R182" t="n">
+        <v>2.463768115942029</v>
+      </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
@@ -36255,9 +36528,12 @@
       <c r="O184" t="n">
         <v>32</v>
       </c>
+      <c r="R184" t="n">
+        <v>1.159420289855073</v>
+      </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U184" t="inlineStr">
@@ -36645,9 +36921,12 @@
       <c r="O186" t="n">
         <v>195</v>
       </c>
+      <c r="R186" t="n">
+        <v>7.065217391304347</v>
+      </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">
@@ -37035,9 +37314,12 @@
       <c r="O188" t="n">
         <v>129</v>
       </c>
+      <c r="R188" t="n">
+        <v>4.673913043478261</v>
+      </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
@@ -37425,9 +37707,12 @@
       <c r="O190" t="n">
         <v>4</v>
       </c>
+      <c r="R190" t="n">
+        <v>0.1449275362318841</v>
+      </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U190" t="inlineStr">
@@ -37815,9 +38100,12 @@
       <c r="O192" t="n">
         <v>6</v>
       </c>
+      <c r="R192" t="n">
+        <v>0.2173913043478261</v>
+      </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
@@ -38205,9 +38493,12 @@
       <c r="O194" t="n">
         <v>1</v>
       </c>
+      <c r="R194" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U194" t="inlineStr">
@@ -38595,9 +38886,12 @@
       <c r="O196" t="n">
         <v>118</v>
       </c>
+      <c r="R196" t="n">
+        <v>4.275362318840579</v>
+      </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
@@ -38985,9 +39279,12 @@
       <c r="O198" t="n">
         <v>3</v>
       </c>
+      <c r="R198" t="n">
+        <v>0.108695652173913</v>
+      </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U198" t="inlineStr">
@@ -39375,9 +39672,12 @@
       <c r="O200" t="n">
         <v>5</v>
       </c>
+      <c r="R200" t="n">
+        <v>0.1811594202898551</v>
+      </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U200" t="inlineStr">
@@ -39765,9 +40065,12 @@
       <c r="O202" t="n">
         <v>81</v>
       </c>
+      <c r="R202" t="n">
+        <v>2.934782608695652</v>
+      </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
@@ -40155,9 +40458,12 @@
       <c r="O204" t="n">
         <v>17</v>
       </c>
+      <c r="R204" t="n">
+        <v>0.6159420289855072</v>
+      </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
@@ -40545,9 +40851,12 @@
       <c r="O206" t="n">
         <v>1</v>
       </c>
+      <c r="R206" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
@@ -40935,9 +41244,12 @@
       <c r="O208" t="n">
         <v>108</v>
       </c>
+      <c r="R208" t="n">
+        <v>3.91304347826087</v>
+      </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
@@ -41325,9 +41637,12 @@
       <c r="O210" t="n">
         <v>79</v>
       </c>
+      <c r="R210" t="n">
+        <v>2.86231884057971</v>
+      </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U210" t="inlineStr">
@@ -41715,9 +42030,12 @@
       <c r="O212" t="n">
         <v>1</v>
       </c>
+      <c r="R212" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -42105,9 +42423,12 @@
       <c r="O214" t="n">
         <v>10</v>
       </c>
+      <c r="R214" t="n">
+        <v>0.3623188405797101</v>
+      </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
@@ -42495,9 +42816,12 @@
       <c r="O216" t="n">
         <v>2</v>
       </c>
+      <c r="R216" t="n">
+        <v>0.07246376811594203</v>
+      </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
@@ -42885,9 +43209,12 @@
       <c r="O218" t="n">
         <v>34</v>
       </c>
+      <c r="R218" t="n">
+        <v>1.231884057971014</v>
+      </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U218" t="inlineStr">
@@ -43275,9 +43602,12 @@
       <c r="O220" t="n">
         <v>8</v>
       </c>
+      <c r="R220" t="n">
+        <v>0.2898550724637681</v>
+      </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
@@ -43665,9 +43995,12 @@
       <c r="O222" t="n">
         <v>49</v>
       </c>
+      <c r="R222" t="n">
+        <v>1.77536231884058</v>
+      </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
@@ -44055,9 +44388,12 @@
       <c r="O224" t="n">
         <v>14</v>
       </c>
+      <c r="R224" t="n">
+        <v>0.5072463768115942</v>
+      </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U224" t="inlineStr">
@@ -44445,9 +44781,12 @@
       <c r="O226" t="n">
         <v>58</v>
       </c>
+      <c r="R226" t="n">
+        <v>2.101449275362319</v>
+      </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
@@ -44835,9 +45174,12 @@
       <c r="O228" t="n">
         <v>63</v>
       </c>
+      <c r="R228" t="n">
+        <v>2.282608695652174</v>
+      </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U228" t="inlineStr">
@@ -45225,9 +45567,12 @@
       <c r="O230" t="n">
         <v>5</v>
       </c>
+      <c r="R230" t="n">
+        <v>0.1811594202898551</v>
+      </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
@@ -45615,9 +45960,12 @@
       <c r="O232" t="n">
         <v>4</v>
       </c>
+      <c r="R232" t="n">
+        <v>0.1449275362318841</v>
+      </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
@@ -46005,9 +46353,12 @@
       <c r="O234" t="n">
         <v>6</v>
       </c>
+      <c r="R234" t="n">
+        <v>0.2173913043478261</v>
+      </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">
@@ -46395,9 +46746,12 @@
       <c r="O236" t="n">
         <v>1</v>
       </c>
+      <c r="R236" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
@@ -46785,9 +47139,12 @@
       <c r="O238" t="n">
         <v>3</v>
       </c>
+      <c r="R238" t="n">
+        <v>0.108695652173913</v>
+      </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U238" t="inlineStr">
@@ -47175,9 +47532,12 @@
       <c r="O240" t="n">
         <v>2</v>
       </c>
+      <c r="R240" t="n">
+        <v>0.07246376811594203</v>
+      </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
@@ -47565,9 +47925,12 @@
       <c r="O242" t="n">
         <v>28</v>
       </c>
+      <c r="R242" t="n">
+        <v>1.014492753623188</v>
+      </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
@@ -47955,9 +48318,12 @@
       <c r="O244" t="n">
         <v>1</v>
       </c>
+      <c r="R244" t="n">
+        <v>0.03623188405797102</v>
+      </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
